--- a/reports/pdf_change_20260921.xlsx
+++ b/reports/pdf_change_20260921.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억   ·   현금 31억(0.7%)      당일 2026-09-21  vs  전영업일 2026-09-18      매수 4종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,665억      당일 2026-09-21  vs  전영업일 2026-09-18      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>70</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1485484742</v>
+        <v>1481031822</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>이랜텍</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2299097948</v>
+        <v>-225927213</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.77%→1.33%</t>
+          <t>0.12%→0.07%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>122→89</t>
+          <t>80→47</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1389789094</v>
+        <v>1385623033</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -728,23 +728,23 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>이랜텍</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-226606493</v>
+        <v>-2292206124</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.07%</t>
+          <t>1.77%→1.33%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>80→47</t>
+          <t>122→89</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>457457228</v>
+        <v>456085945</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-18</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1322521861</v>
+        <v>-1318557441</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>678177839</v>
+        <v>676144919</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-15</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-439188969</v>
+        <v>-437872447</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억   ·   현금 59억(1.8%)      당일 2026-09-21  vs  전영업일 2026-09-18      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,342억      당일 2026-09-21  vs  전영업일 2026-09-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -863,7 +863,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억   ·   현금 42억(1.6%)      당일 2026-09-21  vs  전영업일 2026-09-18      매수 1종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,563억      당일 2026-09-21  vs  전영업일 2026-09-18      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -959,7 +959,7 @@
         <v>100</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3696440108</v>
+        <v>3696438699</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>-133</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1224531036</v>
+        <v>-1224530569</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>-59</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1193056735</v>
+        <v>-1193056280</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>-16</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1234147236</v>
+        <v>-1234146766</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억   ·   현금 11억(0.6%)      당일 2026-09-21  vs  전영업일 2026-09-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,903억      당일 2026-09-21  vs  전영업일 2026-09-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1076,7 +1076,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 2억(0.5%)      당일 2026-09-21  vs  전영업일 2026-09-18      매수 1종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 284억      당일 2026-09-21  vs  전영업일 2026-09-18      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1172,11 +1172,11 @@
         <v>39</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>93502500</v>
+        <v>92410553</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>6.91%→7.24%</t>
+          <t>6.72%→7.04%</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1193,11 +1193,11 @@
         <v>-42</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-28518000</v>
+        <v>-30252617</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>7.27%→7.16%</t>
+          <t>7.59%→7.48%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1221,11 +1221,11 @@
         <v>-32</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-52864000</v>
+        <v>-55664032</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>5.31%→5.12%</t>
+          <t>5.50%→5.31%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1249,11 +1249,11 @@
         <v>-15</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-30660000</v>
+        <v>-32392519</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.65%→2.54%</t>
+          <t>2.76%→2.64%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">

--- a/reports/pdf_change_20260921.xlsx
+++ b/reports/pdf_change_20260921.xlsx
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>이랜텍</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-225927213</v>
+        <v>-2292206124</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.07%</t>
+          <t>1.77%→1.33%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>80→47</t>
+          <t>122→89</t>
         </is>
       </c>
     </row>
@@ -728,46 +728,46 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>이랜텍</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2292206124</v>
+        <v>-225927213</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>1.77%→1.33%</t>
+          <t>0.12%→0.07%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>122→89</t>
+          <t>80→47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>에이프릴바이오  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>25</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>456085945</v>
+        <v>676144919</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.10%</t>
+          <t>0.34%→0.47%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>0→25</t>
+          <t>56→81</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이프릴바이오  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>25</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>676144919</v>
+        <v>456085945</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.34%→0.47%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>56→81</t>
+          <t>0→25</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
